--- a/报价工作流DA梳理.xlsx
+++ b/报价工作流DA梳理.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1544,7 +1544,7 @@
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>完成时的表单快照</t>
+          <t>完成时的表单快照(前端 JSON.stringify,写入时 ::jsonb;非法/空则存 NULL)</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n"/>
+      <c r="A66" s="7" t="n"/>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="4" t="inlineStr">
@@ -2362,22 +2362,321 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="7" t="n"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>cpq_wf_message</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>站内消息(任务流提醒;DA原清单外的补充表)</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>message_id</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>消息ID</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n"/>
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>收件人</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>FK-&gt;cpq_wf_user.user_id</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n"/>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>msg_type</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>消息类型</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>varchar(24)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>task_sent=我发出的任务 / task_received=收到新任务 / task_claimed=任务被领取</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n"/>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>varchar(255)</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>正文</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>varchar(1000)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n"/>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>card_id</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>关联卡片</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>FK-&gt;cpq_wf_card.card_id</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>可空</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>task_id</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>关联任务</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>FK-&gt;cpq_wf_task.task_id</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>可空</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n"/>
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>会话ID</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>varchar(32)</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>点消息可直达该卡片工作台</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>step_no</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>相关步骤</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n"/>
+      <c r="B76" s="7" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>is_read</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>是否已读</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>默认 false</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n"/>
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="B53:B61"/>
     <mergeCell ref="B39:B52"/>
     <mergeCell ref="C29:C38"/>
     <mergeCell ref="B62:B66"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B17:B28"/>
-    <mergeCell ref="A2:A66"/>
+    <mergeCell ref="A2:A77"/>
     <mergeCell ref="C2:C11"/>
     <mergeCell ref="B12:B16"/>
     <mergeCell ref="C17:C28"/>
     <mergeCell ref="C12:C16"/>
     <mergeCell ref="B29:B38"/>
     <mergeCell ref="C53:C61"/>
+    <mergeCell ref="B67:B77"/>
     <mergeCell ref="C39:C52"/>
+    <mergeCell ref="C67:C77"/>
     <mergeCell ref="C62:C66"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
